--- a/1-LATEX/2-DADOS/3-OUTPUT/ranking_lnRR.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/ranking_lnRR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,25 +412,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vulnerabilidade Jurídica</t>
+          <t>Exposicao Climatica</t>
         </is>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E2">
-        <v>-0.2787297834861159</v>
+        <v>0.2796759127099698</v>
       </c>
       <c r="F2">
-        <v>0.1053211656444903</v>
+        <v>0.06830923323932046</v>
       </c>
       <c r="G2">
-        <v>-24.3</v>
+        <v>32.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="I2">
-        <v>0.471</v>
+        <v>0.34</v>
       </c>
       <c r="J2">
-        <v>0.471</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="3">
@@ -450,25 +450,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Organização Social</t>
+          <t>Vulnerabilidade Juridica</t>
         </is>
       </c>
       <c r="D3">
         <v>37</v>
       </c>
       <c r="E3">
-        <v>0.1716000516464709</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="F3">
-        <v>0.1058399698656821</v>
+        <v>0.1053211656444903</v>
       </c>
       <c r="G3">
-        <v>18.7</v>
+        <v>-24.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="I3">
-        <v>0.29</v>
+        <v>0.339</v>
       </c>
       <c r="J3">
-        <v>0.29</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="4">
@@ -488,25 +488,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singularidade Territorial</t>
+          <t>Organizacao Social</t>
         </is>
       </c>
       <c r="D4">
         <v>37</v>
       </c>
       <c r="E4">
-        <v>0.0715762333288117</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="F4">
-        <v>0.07407978426245312</v>
+        <v>0.1058399698656821</v>
       </c>
       <c r="G4">
-        <v>7.4</v>
+        <v>18.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="I4">
-        <v>0.121</v>
+        <v>0.209</v>
       </c>
       <c r="J4">
-        <v>0.121</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="5">
@@ -526,25 +526,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complexidade Biocultural</t>
+          <t>Integracao ao Mercado</t>
         </is>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E5">
-        <v>0.04486936865596249</v>
+        <v>0.05120757691971459</v>
       </c>
       <c r="F5">
-        <v>0.0506784021094261</v>
+        <v>0.0286313327549371</v>
       </c>
       <c r="G5">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="I5">
-        <v>0.076</v>
+        <v>0.062</v>
       </c>
       <c r="J5">
-        <v>0.076</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="6">
@@ -569,7 +569,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Erosão Intergeracional</t>
+          <t>Erosao Intergeracional</t>
         </is>
       </c>
       <c r="D6">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="J6">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="7">
@@ -602,36 +602,112 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Status de Documentação</t>
+          <t>Complexidade Biocultural</t>
         </is>
       </c>
       <c r="D7">
         <v>37</v>
       </c>
       <c r="E7">
+        <v>0.01655094282820235</v>
+      </c>
+      <c r="F7">
+        <v>0.04715143097179037</v>
+      </c>
+      <c r="G7">
+        <v>1.7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>0.02</v>
+      </c>
+      <c r="J7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Status de Documentacao</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>37</v>
+      </c>
+      <c r="E8">
         <v>0.007406689765167936</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>0.1024738071770136</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>0.7</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Confirmatória (meta-análise completa)</t>
         </is>
       </c>
-      <c r="I7">
-        <v>0.013</v>
-      </c>
-      <c r="J7">
-        <v>0.013</v>
+      <c r="I8">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J8">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vitalidade Linguistica</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>47</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
